--- a/output/pdf_financials_xlsx/SMN.xlsx
+++ b/output/pdf_financials_xlsx/SMN.xlsx
@@ -937,31 +937,31 @@
         <v>0.08323999999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.109982</v>
+        <v>0.948848</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.189565</v>
+        <v>1.685895</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.258863</v>
+        <v>1.578266</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.20446</v>
+        <v>0.855615</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.577036</v>
+        <v>8.29313</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.65165</v>
+        <v>6.033831</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.522742</v>
+        <v>3.948213</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.8917890000000001</v>
+        <v>4.664687</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>1.223699</v>
+        <v>11.0289</v>
       </c>
     </row>
     <row r="11">
@@ -995,31 +995,31 @@
         <v>-0.08323999999999999</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.109982</v>
+        <v>-0.948848</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.189565</v>
+        <v>-1.685895</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.258863</v>
+        <v>-1.578266</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.20446</v>
+        <v>-0.855615</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.577036</v>
+        <v>-8.29313</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.65165</v>
+        <v>-6.033831</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.522742</v>
+        <v>-3.948213</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.8917890000000001</v>
+        <v>-4.664687</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-1.223699</v>
+        <v>-11.0289</v>
       </c>
     </row>
     <row r="12">
@@ -1029,55 +1029,55 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.00839</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004103</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004847</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.005402</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000262</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004553</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000376</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000954</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.001575</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.003989</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.010836</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.002275</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.012346</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.047269</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.049088</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.038431</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.08093599999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1967,55 +1967,55 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.189649</v>
+        <v>-0.198039</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.431159</v>
+        <v>-0.435262</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.165894</v>
+        <v>-1.170741</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.038202</v>
+        <v>-1.043604</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.67458</v>
+        <v>-1.674842</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.657632</v>
+        <v>-1.653079</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.719893</v>
+        <v>-3.719517</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.711755</v>
+        <v>-0.710801</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.960562</v>
+        <v>-0.962137</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.415225</v>
+        <v>-1.419214</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.572513</v>
+        <v>-1.583349</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.8369</v>
+        <v>-0.839175</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-7.502743</v>
+        <v>-7.515089</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.79968</v>
+        <v>-4.846949</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.715074</v>
+        <v>-3.764162</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-4.427088</v>
+        <v>-4.465519</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-8.752471999999999</v>
+        <v>-8.833408</v>
       </c>
     </row>
     <row r="28">
@@ -2083,55 +2083,55 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.189649</v>
+        <v>-0.198039</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.431159</v>
+        <v>-0.435262</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.165894</v>
+        <v>-1.170741</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.010021</v>
+        <v>-1.015423</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.650323</v>
+        <v>-1.650585</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.637101</v>
+        <v>-1.632548</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.701964</v>
+        <v>-3.701588</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.70423</v>
+        <v>-0.703276</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.958219</v>
+        <v>-0.959794</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.413715</v>
+        <v>-1.417704</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.566254</v>
+        <v>-1.57709</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.828774</v>
+        <v>-0.831049</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-7.495744</v>
+        <v>-7.50809</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.791141</v>
+        <v>-4.83841</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.707789</v>
+        <v>-3.756877</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-4.421259</v>
+        <v>-4.45969</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-8.747185</v>
+        <v>-8.828120999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.110413</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.493655</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.460046</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.317823</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.791171</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.245323</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.034435</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.034435</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.126291</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.579424</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.792492</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.411091</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>2.159042</v>
@@ -2506,40 +2506,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.110413</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.493655</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.460046</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.317823</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.178855</v>
+        <v>0.9700260000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.163551</v>
+        <v>0.408874</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.015998</v>
+        <v>0.050433</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.015998</v>
+        <v>0.050433</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.005833</v>
+        <v>0.132124</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.00248</v>
+        <v>1.581904</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.001162</v>
+        <v>0.793654</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.001162</v>
+        <v>0.412253</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>2.159917</v>
@@ -3202,40 +3202,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.110413</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.497512</v>
+        <v>0.003857</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.486962</v>
+        <v>0.026916</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.322731</v>
+        <v>0.004908</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.804858</v>
+        <v>0.013687</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.254031</v>
+        <v>0.008708</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.036886</v>
+        <v>0.002451</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.036886</v>
+        <v>0.002451</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.129464</v>
+        <v>0.003173</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.618031</v>
+        <v>0.038607</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.176876</v>
+        <v>0.384384</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.458938</v>
+        <v>0.047847</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.373681</v>
@@ -9540,7 +9540,11 @@
           <t>Reclamation deposit (Note 5)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10836,7 +10840,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11236,7 +11240,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -12343,7 +12351,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -12761,7 +12769,11 @@
           <t>Reclamation deposit 2,000</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -13888,7 +13900,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -14298,7 +14310,11 @@
           <t>Reclamation deposit (Note 7) 2,000</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -15821,7 +15837,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -16009,7 +16025,11 @@
           <t>Reclamation deposit (Note 6)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -17569,7 +17589,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -17971,7 +17991,11 @@
           <t>Reclamation deposit (Note 4)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -19175,7 +19199,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -19587,7 +19611,11 @@
           <t>RECLAMATION DEPOSIT (Note 5)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
         <v>0.002</v>
       </c>
@@ -21633,7 +21661,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -53299,7 +53331,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -53346,7 +53378,7 @@
         <v>0.948848</v>
       </c>
       <c r="N454" s="5" t="n">
-        <v>-1.685895</v>
+        <v>1.685895</v>
       </c>
       <c r="O454" s="5" t="n">
         <v>1.578266</v>
@@ -53355,19 +53387,19 @@
         <v>0.855615</v>
       </c>
       <c r="Q454" s="5" t="n">
-        <v>-8.29313</v>
+        <v>8.29313</v>
       </c>
       <c r="R454" s="5" t="n">
-        <v>-6.033831</v>
+        <v>6.033831</v>
       </c>
       <c r="S454" s="5" t="n">
-        <v>-3.948213</v>
+        <v>3.948213</v>
       </c>
       <c r="T454" s="5" t="n">
-        <v>-4.664687</v>
+        <v>4.664687</v>
       </c>
       <c r="U454" s="5" t="n">
-        <v>-11.0289</v>
+        <v>11.0289</v>
       </c>
     </row>
     <row r="455">
@@ -53481,7 +53513,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -58407,7 +58439,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -58512,7 +58544,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -60221,7 +60253,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -60324,7 +60356,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -62983,7 +63015,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E552" s="5" t="n">

--- a/output/pdf_financials_xlsx/SMN.xlsx
+++ b/output/pdf_financials_xlsx/SMN.xlsx
@@ -4352,25 +4352,25 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.26271</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.169258</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.036845</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.066112</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.020206</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.024074</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K67" s="3" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
         <v>0.045964</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K68" s="3" t="n">
         <v>0.08597399999999999</v>
@@ -6918,22 +6918,22 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.039266</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.070148</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.016569</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001479</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014621</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000391</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
         <v>-0.003439</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.036839</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>-0.008595999999999999</v>
@@ -8286,22 +8286,22 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.039266</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.070148</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.016569</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001479</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014621</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000391</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -8319,7 +8319,7 @@
         <v>-0.003439</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.036839</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>-0.008595999999999999</v>
@@ -8344,22 +8344,22 @@
         <v>-0.134855</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.294954</v>
+        <v>-0.33422</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.840526</v>
+        <v>-0.910674</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.8148300000000001</v>
+        <v>-0.831399</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.766218</v>
+        <v>-0.767697</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.594628</v>
+        <v>-0.609249</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.314618</v>
+        <v>-0.315009</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-0.543915</v>
@@ -8377,7 +8377,7 @@
         <v>-0.783126</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-6.682763</v>
+        <v>-6.719602</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-5.578083</v>
@@ -23306,7 +23306,11 @@
           <t>Shares issued for cash 141,196,666 12,466,204 364,191</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -27512,7 +27516,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -31619,7 +31627,11 @@
           <t>Shares issued for cash (Note 8) 3,738,334 336,450 112,150</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -33017,7 +33029,11 @@
           <t>Private placement (Note 7(b)) 8,444,000 1,435,480 84,440</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -35441,7 +35457,11 @@
           <t>Private placement 8,444,000 1,435,480 84,440</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -36449,7 +36469,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -36655,7 +36679,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -41750,7 +41778,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -50493,7 +50525,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E424" s="5" t="n">
         <v>-0.043125</v>
       </c>
@@ -64536,7 +64572,11 @@
           <t>FUTURE INCOME TAX RECOVERY (Note 13)</t>
         </is>
       </c>
-      <c r="D567" t="inlineStr"/>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E567" s="5" t="n">
         <v>0.043125</v>
       </c>
